--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1257,10 +1257,10 @@
         <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45980.89583333334</v>
+        <v>45980.85416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,14 +1373,14 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.2</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1561,6 +1561,125 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
+        <v>45980.89583333334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
         <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
         <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45980.85416666666</v>
+        <v>45980.8125</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45980.89583333334</v>
+        <v>45980.85416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,75 +1611,194 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>45980.89583333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,14 +1492,14 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.2</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
         <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,14 +1730,14 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.2</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
         <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.95</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>2.94</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,14 +1492,14 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.94</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>3.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N11" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,14 +1730,14 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.94</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.94</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,14 +1492,14 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.94</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.94</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,40 +1144,40 @@
         <v>9.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
         <v>1.67</v>
@@ -1186,22 +1186,22 @@
         <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1263,40 +1263,40 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
         <v>2.35</v>
@@ -1305,22 +1305,22 @@
         <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45980.8125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>2.52</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.4</v>
+        <v>5.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>3.22</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>5.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.8</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.42</v>
+        <v>9.4</v>
       </c>
       <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.49</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="V7" t="n">
-        <v>9.199999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.15</v>
       </c>
-      <c r="AE7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.88</v>
+        <v>3.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45980.8125</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,13 +1144,13 @@
         <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.42</v>
+        <v>5.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.49</v>
@@ -1266,10 +1266,10 @@
         <v>1.67</v>
       </c>
       <c r="P7" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
@@ -1296,7 +1296,7 @@
         <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="AA7" t="n">
         <v>1.67</v>
@@ -1308,16 +1308,16 @@
         <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF7" t="n">
         <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
         <v>3.8</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>4.7</v>
+        <v>2.72</v>
       </c>
       <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.26</v>
+        <v>1.72</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1739,16 +1739,16 @@
         <v>2.94</v>
       </c>
       <c r="O11" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
         <v>2.88</v>
@@ -1757,22 +1757,22 @@
         <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
         <v>1.82</v>
@@ -1781,19 +1781,19 @@
         <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
         <v>1.64</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.5</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q6" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>3.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.15</v>
       </c>
-      <c r="AE6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>3.8</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.67</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45980.8125</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
@@ -1513,7 +1513,7 @@
         <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="T9" t="n">
         <v>3.2</v>
@@ -1525,22 +1525,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
         <v>4.5</v>
@@ -1555,7 +1555,7 @@
         <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
         <v>1.25</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.21</v>
       </c>
-      <c r="O10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AG10" t="n">
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.68</v>
@@ -1156,13 +1156,13 @@
         <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
         <v>5.8</v>
@@ -1180,22 +1180,22 @@
         <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
         <v>2.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
         <v>2.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
         <v>1.15</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>2.47</v>
@@ -1299,10 +1299,10 @@
         <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
         <v>4.3</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>3.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>3.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>3.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>2.69</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.72</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>5.35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.35</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.35</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.49</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.27</v>
-      </c>
       <c r="V7" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45980.8125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.33</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.94</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>3.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>3.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -906,64 +906,64 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45980.625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.35</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.49</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="V6" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>5.35</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T7" t="n">
         <v>3.35</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.8</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45980.8125</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.94</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>3.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>3.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.68</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.33</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -906,64 +906,64 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45980.625</v>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45980.625</v>
+        <v>45980.8125</v>
       </c>
     </row>
     <row r="6">
@@ -1147,10 +1147,10 @@
         <v>1.68</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1159,13 +1159,13 @@
         <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
@@ -1177,7 +1177,7 @@
         <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
         <v>1.67</v>
@@ -1186,7 +1186,7 @@
         <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
         <v>1.39</v>
@@ -1195,13 +1195,13 @@
         <v>2.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45980.8125</v>
+        <v>45980.85416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45980.85416666666</v>
+        <v>45980.89583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="T9" t="n">
         <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
         <v>6.5</v>
@@ -1528,13 +1528,13 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AA9" t="n">
         <v>1.82</v>
@@ -1543,22 +1543,22 @@
         <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
         <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1620,28 +1620,28 @@
         <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
         <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
         <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
@@ -1650,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="AA10" t="n">
         <v>1.92</v>
@@ -1662,7 +1662,7 @@
         <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
         <v>1.26</v>
@@ -1677,128 +1677,9 @@
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45980.89583333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45980</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.01</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.96</v>
+        <v>3.33</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45980.8125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.23</v>
       </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V6" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>2.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>4.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.33</v>
+        <v>1.92</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.98</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
-        <v>4.04</v>
+        <v>2.57</v>
       </c>
       <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>4.04</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.36</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.98</v>
+        <v>3.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10.23</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45980.625</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1012,80 +1012,80 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45980.8125</v>
+        <v>45980.625</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.75</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.46</v>
+        <v>2.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.7</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45980.85416666666</v>
+        <v>45980.8125</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="M8" t="n">
         <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45980.89583333334</v>
+        <v>45980.85416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>3.18</v>
       </c>
       <c r="O9" t="n">
-        <v>4.04</v>
+        <v>2.63</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,75 +1611,194 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>45980.89583333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.75</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
         <v>1.44</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+      <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>10.23</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45980.625</v>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,80 +1012,80 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45980.625</v>
+        <v>45980.8125</v>
       </c>
     </row>
     <row r="6">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
@@ -1159,34 +1159,34 @@
         <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="U6" t="n">
         <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
         <v>3.84</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
         <v>1.35</v>
@@ -1195,13 +1195,13 @@
         <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45980.8125</v>
+        <v>45980.85416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.34</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45980.85416666666</v>
+        <v>45980.89583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
         <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,194 +1611,75 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
         <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
         <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.24</v>
+        <v>3.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG10" t="n">
         <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45980.89583333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45980</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI11" s="3" t="n">
         <v>45980.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="U5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
         <v>11</v>
@@ -1055,28 +1055,28 @@
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG5" t="n">
         <v>1.32</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.98</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
         <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
         <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.24</v>
+        <v>3.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.74</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>6.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45980.33333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
         <v>1.64</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.88</v>
+        <v>3.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45980.8125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.74</v>
+        <v>2.53</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>5.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="T6" t="n">
-        <v>2.53</v>
+        <v>3.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>6.1</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.84</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
         <v>7</v>
@@ -1409,37 +1409,37 @@
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.24</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>3.94</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>1.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.74</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>6.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.05</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
         <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.63</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>2.94</v>
+        <v>3.44</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>3.44</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.79</v>
+        <v>3.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.09</v>
+        <v>1.77</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -662,19 +662,19 @@
         <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="O2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -704,10 +704,10 @@
         <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.05</v>
@@ -719,7 +719,7 @@
         <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
         <v>1.2</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="P5" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>5.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.57</v>
+        <v>1.89</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45980.8125</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>3.76</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.26</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>4.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.98</v>
+        <v>2.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.94</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.82</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>4.25</v>
+        <v>2.49</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>4.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.44</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>3.44</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.69</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.94</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O8" t="n">
-        <v>4.65</v>
+        <v>2.66</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.69</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.39</v>
-      </c>
       <c r="T8" t="n">
-        <v>3.34</v>
+        <v>3.09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.77</v>
+        <v>3.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2.49</v>
+        <v>4.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.14</v>
+        <v>2.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.39</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.24</v>
+        <v>4.77</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.72</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.54</v>
+        <v>4.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.84</v>
+        <v>3.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -655,77 +655,77 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.9</v>
+        <v>3.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="N2" t="n">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="O2" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.31</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V2" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45980.33333333334</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.58</v>
+        <v>4.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="T5" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC5" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45980.8125</v>
@@ -1144,40 +1144,40 @@
         <v>9.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.66</v>
+        <v>8.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AA6" t="n">
         <v>1.76</v>
@@ -1186,22 +1186,22 @@
         <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="O8" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.54</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.82</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>4.65</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.69</v>
+        <v>4.11</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.77</v>
+        <v>3.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.14</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.81</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.02</v>
       </c>
       <c r="U10" t="n">
         <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,31 +1016,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="T5" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
         <v>1.28</v>
@@ -1052,37 +1052,37 @@
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="AD5" t="n">
         <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45980.8125</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.82</v>
       </c>
       <c r="P6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U6" t="n">
         <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1177,19 +1177,19 @@
         <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
         <v>2.29</v>
@@ -1198,10 +1198,10 @@
         <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45980.8125</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
         <v>3.3</v>
@@ -1403,43 +1403,43 @@
         <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
         <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.11</v>
+        <v>3.69</v>
       </c>
       <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.3</v>
       </c>
       <c r="Z9" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC9" t="n">
         <v>3.4</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.24</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.12</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.11</v>
-      </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
         <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AB10" t="n">
         <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
         <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45980.89583333334</v>

--- a/jogos_2025-11-19.xlsx
+++ b/jogos_2025-11-19.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>2.67</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>3.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.53</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45980.89583333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.15</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.69</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.24</v>
+        <v>2.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>2.53</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45980.89583333334</v>
